--- a/dcf-grader/sample-models/tap-turf-completed-clean.xlsx
+++ b/dcf-grader/sample-models/tap-turf-completed-clean.xlsx
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.85</v>
+        <v>0.41</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.35</v>
+        <v>1.34</v>
       </c>
       <c r="E20" s="10">
         <f>C20/(1+(1-$C$14)*D20)</f>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E21" s="10">
         <f>C21/(1+(1-$C$14)*D21)</f>
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.3</v>
+        <v>1.13</v>
       </c>
       <c r="E22" s="10">
         <f>C22/(1+(1-$C$14)*D22)</f>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.8</v>
+        <v>2.14</v>
       </c>
       <c r="E23" s="10">
         <f>C23/(1+(1-$C$14)*D23)</f>
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>0.95</v>
+        <v>0.42</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="E24" s="10">
         <f>C24/(1+(1-$C$14)*D24)</f>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.0425</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="28">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="29">

--- a/dcf-grader/sample-models/tap-turf-completed-clean.xlsx
+++ b/dcf-grader/sample-models/tap-turf-completed-clean.xlsx
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="E21" s="10">
         <f>C21/(1+(1-$C$14)*D21)</f>
